--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4140,7 +4140,7 @@
         <v>136240267</v>
       </c>
       <c r="B34" t="n">
-        <v>57847</v>
+        <v>57849</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ90"/>
+  <dimension ref="A1:AZ91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4937,32 +4937,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>132477079</v>
+        <v>137095175</v>
       </c>
       <c r="B41" t="n">
-        <v>58131</v>
+        <v>58169</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4973,24 +4973,20 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451648</v>
+        <v>451853</v>
       </c>
       <c r="R41" t="n">
-        <v>6795608</v>
+        <v>6795315</v>
       </c>
       <c r="S41" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5014,12 +5010,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5045,66 +5041,66 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477079</t>
+          <t>https://artportalen.se/Sighting/137095175</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>125109158</v>
+        <v>132477079</v>
       </c>
       <c r="B42" t="n">
-        <v>56522</v>
+        <v>58131</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>206004</v>
+        <v>103023</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451891</v>
+        <v>451648</v>
       </c>
       <c r="R42" t="n">
-        <v>6795458</v>
+        <v>6795608</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5128,12 +5124,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5159,16 +5155,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125109158</t>
+          <t>https://artportalen.se/Sighting/132477079</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>132477114</v>
+        <v>125109158</v>
       </c>
       <c r="B43" t="n">
-        <v>56539</v>
+        <v>56522</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5205,24 +5201,20 @@
           <t>gående/springande</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451648</v>
+        <v>451891</v>
       </c>
       <c r="R43" t="n">
-        <v>6795608</v>
+        <v>6795458</v>
       </c>
       <c r="S43" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5246,12 +5238,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5277,33 +5269,33 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477114</t>
+          <t>https://artportalen.se/Sighting/125109158</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132918321</v>
+        <v>132477114</v>
       </c>
       <c r="B44" t="n">
-        <v>58839</v>
+        <v>56539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5313,15 +5305,14 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>gående/springande</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5335,13 +5326,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>451860</v>
+        <v>451648</v>
       </c>
       <c r="R44" t="n">
-        <v>6795469</v>
+        <v>6795608</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5365,12 +5356,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5379,7 +5370,6 @@
       <c r="AE44" t="b">
         <v>0</v>
       </c>
-      <c r="AF44" t="inlineStr"/>
       <c r="AG44" t="b">
         <v>0</v>
       </c>
@@ -5397,16 +5387,16 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132918321</t>
+          <t>https://artportalen.se/Sighting/132477114</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134446393</v>
+        <v>132918321</v>
       </c>
       <c r="B45" t="n">
-        <v>99103</v>
+        <v>58839</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5414,45 +5404,54 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>219788</v>
+        <v>208249</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451856</v>
+        <v>451860</v>
       </c>
       <c r="R45" t="n">
-        <v>6795459</v>
+        <v>6795469</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5476,12 +5475,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5508,16 +5507,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446393</t>
+          <t>https://artportalen.se/Sighting/132918321</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133997108</v>
+        <v>134446393</v>
       </c>
       <c r="B46" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,16 +5524,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5544,22 +5543,26 @@
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451891</v>
+        <v>451856</v>
       </c>
       <c r="R46" t="n">
-        <v>6795458</v>
+        <v>6795459</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5583,12 +5586,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5615,13 +5618,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997108</t>
+          <t>https://artportalen.se/Sighting/134446393</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133997151</v>
+        <v>133997108</v>
       </c>
       <c r="B47" t="n">
         <v>99112</v>
@@ -5656,17 +5659,17 @@
       <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451900</v>
+        <v>451891</v>
       </c>
       <c r="R47" t="n">
-        <v>6795487</v>
+        <v>6795458</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5722,13 +5725,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997151</t>
+          <t>https://artportalen.se/Sighting/133997108</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134446465</v>
+        <v>133997151</v>
       </c>
       <c r="B48" t="n">
         <v>99112</v>
@@ -5758,23 +5761,19 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451867</v>
+        <v>451900</v>
       </c>
       <c r="R48" t="n">
-        <v>6795467</v>
+        <v>6795487</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5801,12 +5800,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5833,13 +5832,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446465</t>
+          <t>https://artportalen.se/Sighting/133997151</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134452196</v>
+        <v>134446465</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -5869,7 +5868,11 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5878,10 +5881,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451858</v>
+        <v>451867</v>
       </c>
       <c r="R49" t="n">
-        <v>6795529</v>
+        <v>6795467</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5940,13 +5943,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452196</t>
+          <t>https://artportalen.se/Sighting/134446465</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134452278</v>
+        <v>134452196</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -5985,7 +5988,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451878</v>
+        <v>451858</v>
       </c>
       <c r="R50" t="n">
         <v>6795529</v>
@@ -6047,13 +6050,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452278</t>
+          <t>https://artportalen.se/Sighting/134452196</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134452340</v>
+        <v>134452278</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6092,10 +6095,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451934</v>
+        <v>451878</v>
       </c>
       <c r="R51" t="n">
-        <v>6795489</v>
+        <v>6795529</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6154,13 +6157,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452340</t>
+          <t>https://artportalen.se/Sighting/134452278</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134452392</v>
+        <v>134452340</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6199,10 +6202,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451845</v>
+        <v>451934</v>
       </c>
       <c r="R52" t="n">
-        <v>6795346</v>
+        <v>6795489</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6261,13 +6264,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452392</t>
+          <t>https://artportalen.se/Sighting/134452340</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134452446</v>
+        <v>134452392</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6306,10 +6309,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451876</v>
+        <v>451845</v>
       </c>
       <c r="R53" t="n">
-        <v>6795437</v>
+        <v>6795346</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6368,13 +6371,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452446</t>
+          <t>https://artportalen.se/Sighting/134452392</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134452468</v>
+        <v>134452446</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6413,10 +6416,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451872</v>
+        <v>451876</v>
       </c>
       <c r="R54" t="n">
-        <v>6795459</v>
+        <v>6795437</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6475,13 +6478,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452468</t>
+          <t>https://artportalen.se/Sighting/134452446</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134470975</v>
+        <v>134452468</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6509,33 +6512,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451828</v>
+        <v>451872</v>
       </c>
       <c r="R55" t="n">
-        <v>6795362</v>
+        <v>6795459</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6562,12 +6553,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6594,13 +6585,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470975</t>
+          <t>https://artportalen.se/Sighting/134452468</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134471030</v>
+        <v>134470975</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6628,21 +6619,33 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451822</v>
+        <v>451828</v>
       </c>
       <c r="R56" t="n">
-        <v>6795403</v>
+        <v>6795362</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6701,13 +6704,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471030</t>
+          <t>https://artportalen.se/Sighting/134470975</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134471064</v>
+        <v>134471030</v>
       </c>
       <c r="B57" t="n">
         <v>99112</v>
@@ -6746,10 +6749,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451754</v>
+        <v>451822</v>
       </c>
       <c r="R57" t="n">
-        <v>6795474</v>
+        <v>6795403</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6808,13 +6811,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471064</t>
+          <t>https://artportalen.se/Sighting/134471030</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134471377</v>
+        <v>134471064</v>
       </c>
       <c r="B58" t="n">
         <v>99112</v>
@@ -6853,10 +6856,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451524</v>
+        <v>451754</v>
       </c>
       <c r="R58" t="n">
-        <v>6795576</v>
+        <v>6795474</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6915,13 +6918,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471377</t>
+          <t>https://artportalen.se/Sighting/134471064</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134519430</v>
+        <v>134471377</v>
       </c>
       <c r="B59" t="n">
         <v>99112</v>
@@ -6950,19 +6953,23 @@
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451846</v>
+        <v>451524</v>
       </c>
       <c r="R59" t="n">
-        <v>6795506</v>
+        <v>6795576</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6986,22 +6993,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7010,33 +7007,34 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519430</t>
+          <t>https://artportalen.se/Sighting/134471377</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135087727</v>
+        <v>134519430</v>
       </c>
       <c r="B60" t="n">
-        <v>99186</v>
+        <v>99112</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7062,23 +7060,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451853</v>
+        <v>451846</v>
       </c>
       <c r="R60" t="n">
-        <v>6795315</v>
+        <v>6795506</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7102,12 +7096,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7116,34 +7120,33 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135087727</t>
+          <t>https://artportalen.se/Sighting/134519430</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135940067</v>
+        <v>135087727</v>
       </c>
       <c r="B61" t="n">
-        <v>99259</v>
+        <v>99186</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7168,29 +7171,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451650</v>
+        <v>451853</v>
       </c>
       <c r="R61" t="n">
-        <v>6795625</v>
+        <v>6795315</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7217,12 +7212,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7249,16 +7244,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135940067</t>
+          <t>https://artportalen.se/Sighting/135087727</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135370390</v>
+        <v>135940067</v>
       </c>
       <c r="B62" t="n">
-        <v>99175</v>
+        <v>99259</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7266,42 +7261,46 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451924</v>
+        <v>451650</v>
       </c>
       <c r="R62" t="n">
-        <v>6795456</v>
+        <v>6795625</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7328,17 +7327,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>I källmiljö</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7365,16 +7359,16 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370390</t>
+          <t>https://artportalen.se/Sighting/135940067</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135896094</v>
+        <v>135370390</v>
       </c>
       <c r="B63" t="n">
-        <v>99241</v>
+        <v>99175</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7401,19 +7395,23 @@
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451940</v>
+        <v>451924</v>
       </c>
       <c r="R63" t="n">
-        <v>6795495</v>
+        <v>6795456</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7440,12 +7438,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>I källmiljö</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7472,16 +7475,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896094</t>
+          <t>https://artportalen.se/Sighting/135370390</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135384823</v>
+        <v>135896094</v>
       </c>
       <c r="B64" t="n">
-        <v>108294</v>
+        <v>99241</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7489,21 +7492,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220083</v>
+        <v>219795</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7513,14 +7516,14 @@
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451640</v>
+        <v>451940</v>
       </c>
       <c r="R64" t="n">
-        <v>6795589</v>
+        <v>6795495</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7547,17 +7550,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Invid källbäck</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7584,16 +7582,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384823</t>
+          <t>https://artportalen.se/Sighting/135896094</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>134446457</v>
+        <v>135384823</v>
       </c>
       <c r="B65" t="n">
-        <v>99099</v>
+        <v>108294</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7601,30 +7599,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220093</v>
+        <v>220083</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
@@ -7633,10 +7627,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451867</v>
+        <v>451640</v>
       </c>
       <c r="R65" t="n">
-        <v>6795467</v>
+        <v>6795589</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7663,12 +7657,17 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Invid källbäck</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7695,13 +7694,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446457</t>
+          <t>https://artportalen.se/Sighting/135384823</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134452308</v>
+        <v>134446457</v>
       </c>
       <c r="B66" t="n">
         <v>99099</v>
@@ -7744,10 +7743,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451924</v>
+        <v>451867</v>
       </c>
       <c r="R66" t="n">
-        <v>6795490</v>
+        <v>6795467</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7806,13 +7805,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452308</t>
+          <t>https://artportalen.se/Sighting/134446457</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134471116</v>
+        <v>134452308</v>
       </c>
       <c r="B67" t="n">
         <v>99099</v>
@@ -7842,7 +7841,11 @@
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -7851,10 +7854,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451657</v>
+        <v>451924</v>
       </c>
       <c r="R67" t="n">
-        <v>6795504</v>
+        <v>6795490</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7881,12 +7884,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7913,13 +7916,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471116</t>
+          <t>https://artportalen.se/Sighting/134452308</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134471163</v>
+        <v>134471116</v>
       </c>
       <c r="B68" t="n">
         <v>99099</v>
@@ -7958,10 +7961,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451656</v>
+        <v>451657</v>
       </c>
       <c r="R68" t="n">
-        <v>6795514</v>
+        <v>6795504</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8020,13 +8023,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471163</t>
+          <t>https://artportalen.se/Sighting/134471116</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134471374</v>
+        <v>134471163</v>
       </c>
       <c r="B69" t="n">
         <v>99099</v>
@@ -8065,10 +8068,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451524</v>
+        <v>451656</v>
       </c>
       <c r="R69" t="n">
-        <v>6795576</v>
+        <v>6795514</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8127,16 +8130,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471374</t>
+          <t>https://artportalen.se/Sighting/134471163</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134471215</v>
+        <v>134471374</v>
       </c>
       <c r="B70" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8144,21 +8147,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8168,14 +8171,14 @@
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451641</v>
+        <v>451524</v>
       </c>
       <c r="R70" t="n">
-        <v>6795575</v>
+        <v>6795576</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8234,13 +8237,13 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471215</t>
+          <t>https://artportalen.se/Sighting/134471374</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134471223</v>
+        <v>134471215</v>
       </c>
       <c r="B71" t="n">
         <v>108274</v>
@@ -8275,14 +8278,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451640</v>
+        <v>451641</v>
       </c>
       <c r="R71" t="n">
-        <v>6795589</v>
+        <v>6795575</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8341,13 +8344,13 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471223</t>
+          <t>https://artportalen.se/Sighting/134471215</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134471252</v>
+        <v>134471223</v>
       </c>
       <c r="B72" t="n">
         <v>108274</v>
@@ -8386,10 +8389,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451628</v>
+        <v>451640</v>
       </c>
       <c r="R72" t="n">
-        <v>6795600</v>
+        <v>6795589</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8448,60 +8451,55 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471252</t>
+          <t>https://artportalen.se/Sighting/134471223</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119623430</v>
+        <v>134471252</v>
       </c>
       <c r="B73" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>452010</v>
+        <v>451628</v>
       </c>
       <c r="R73" t="n">
-        <v>6795395</v>
+        <v>6795600</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8528,12 +8526,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8542,30 +8540,31 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623430</t>
+          <t>https://artportalen.se/Sighting/134471252</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120455163</v>
+        <v>119623430</v>
       </c>
       <c r="B74" t="n">
         <v>99118</v>
@@ -8595,7 +8594,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8603,19 +8602,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452004</v>
+        <v>452010</v>
       </c>
       <c r="R74" t="n">
-        <v>6795386</v>
+        <v>6795395</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8642,12 +8638,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8656,31 +8652,30 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120455163</t>
+          <t>https://artportalen.se/Sighting/119623430</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120493954</v>
+        <v>120455163</v>
       </c>
       <c r="B75" t="n">
         <v>99118</v>
@@ -8710,7 +8705,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -8723,14 +8718,14 @@
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>451990</v>
+        <v>452004</v>
       </c>
       <c r="R75" t="n">
-        <v>6795420</v>
+        <v>6795386</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8757,12 +8752,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8789,16 +8784,16 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493954</t>
+          <t>https://artportalen.se/Sighting/120455163</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133997095</v>
+        <v>120493954</v>
       </c>
       <c r="B76" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8825,12 +8820,12 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K76" t="inlineStr"/>
@@ -8838,14 +8833,14 @@
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451903</v>
+        <v>451990</v>
       </c>
       <c r="R76" t="n">
-        <v>6795472</v>
+        <v>6795420</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8872,12 +8867,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8904,13 +8899,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997095</t>
+          <t>https://artportalen.se/Sighting/120493954</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133997219</v>
+        <v>133997095</v>
       </c>
       <c r="B77" t="n">
         <v>99195</v>
@@ -8940,7 +8935,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -8957,10 +8952,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451888</v>
+        <v>451903</v>
       </c>
       <c r="R77" t="n">
-        <v>6795475</v>
+        <v>6795472</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9019,51 +9014,63 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997219</t>
+          <t>https://artportalen.se/Sighting/133997095</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119622912</v>
+        <v>133997219</v>
       </c>
       <c r="B78" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>452035</v>
+        <v>451888</v>
       </c>
       <c r="R78" t="n">
-        <v>6795377</v>
+        <v>6795475</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9090,12 +9097,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9104,30 +9111,31 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119622912</t>
+          <t>https://artportalen.se/Sighting/133997219</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119623971</v>
+        <v>119622912</v>
       </c>
       <c r="B79" t="n">
         <v>106229</v>
@@ -9162,10 +9170,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>451957</v>
+        <v>452035</v>
       </c>
       <c r="R79" t="n">
-        <v>6795424</v>
+        <v>6795377</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9223,16 +9231,16 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623971</t>
+          <t>https://artportalen.se/Sighting/119622912</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>135896078</v>
+        <v>119623971</v>
       </c>
       <c r="B80" t="n">
-        <v>106468</v>
+        <v>106229</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9258,20 +9266,16 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>452073</v>
+        <v>451957</v>
       </c>
       <c r="R80" t="n">
-        <v>6795385</v>
+        <v>6795424</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9298,12 +9302,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9312,34 +9316,33 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896078</t>
+          <t>https://artportalen.se/Sighting/119623971</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134452234</v>
+        <v>135896078</v>
       </c>
       <c r="B81" t="n">
-        <v>98060</v>
+        <v>106468</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9347,21 +9350,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9371,14 +9374,14 @@
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>451878</v>
+        <v>452073</v>
       </c>
       <c r="R81" t="n">
-        <v>6795529</v>
+        <v>6795385</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9405,12 +9408,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9437,13 +9440,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452234</t>
+          <t>https://artportalen.se/Sighting/135896078</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134452406</v>
+        <v>134452234</v>
       </c>
       <c r="B82" t="n">
         <v>98060</v>
@@ -9482,10 +9485,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451858</v>
+        <v>451878</v>
       </c>
       <c r="R82" t="n">
-        <v>6795410</v>
+        <v>6795529</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9544,13 +9547,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452406</t>
+          <t>https://artportalen.se/Sighting/134452234</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134452426</v>
+        <v>134452406</v>
       </c>
       <c r="B83" t="n">
         <v>98060</v>
@@ -9589,10 +9592,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>451875</v>
+        <v>451858</v>
       </c>
       <c r="R83" t="n">
-        <v>6795422</v>
+        <v>6795410</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9651,13 +9654,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452426</t>
+          <t>https://artportalen.se/Sighting/134452406</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134519426</v>
+        <v>134452426</v>
       </c>
       <c r="B84" t="n">
         <v>98060</v>
@@ -9686,19 +9689,23 @@
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>451669</v>
+        <v>451875</v>
       </c>
       <c r="R84" t="n">
-        <v>6795570</v>
+        <v>6795422</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9722,22 +9729,12 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9746,33 +9743,34 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
+      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519426</t>
+          <t>https://artportalen.se/Sighting/134452426</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>135370746</v>
+        <v>134519426</v>
       </c>
       <c r="B85" t="n">
-        <v>98138</v>
+        <v>98060</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9798,23 +9796,19 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>451924</v>
+        <v>451669</v>
       </c>
       <c r="R85" t="n">
-        <v>6795456</v>
+        <v>6795570</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9838,12 +9832,22 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9852,31 +9856,30 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370746</t>
+          <t>https://artportalen.se/Sighting/134519426</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135370757</v>
+        <v>135370746</v>
       </c>
       <c r="B86" t="n">
         <v>98138</v>
@@ -9911,17 +9914,17 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451910</v>
+        <v>451924</v>
       </c>
       <c r="R86" t="n">
-        <v>6795497</v>
+        <v>6795456</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9977,16 +9980,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370757</t>
+          <t>https://artportalen.se/Sighting/135370746</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>134470979</v>
+        <v>135370757</v>
       </c>
       <c r="B87" t="n">
-        <v>99217</v>
+        <v>98138</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9994,21 +9997,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10018,17 +10021,17 @@
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451828</v>
+        <v>451910</v>
       </c>
       <c r="R87" t="n">
-        <v>6795362</v>
+        <v>6795497</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10052,12 +10055,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10084,13 +10087,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470979</t>
+          <t>https://artportalen.se/Sighting/135370757</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134471102</v>
+        <v>134470979</v>
       </c>
       <c r="B88" t="n">
         <v>99217</v>
@@ -10125,14 +10128,14 @@
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>451693</v>
+        <v>451828</v>
       </c>
       <c r="R88" t="n">
-        <v>6795486</v>
+        <v>6795362</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10191,13 +10194,13 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471102</t>
+          <t>https://artportalen.se/Sighting/134470979</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134471378</v>
+        <v>134471102</v>
       </c>
       <c r="B89" t="n">
         <v>99217</v>
@@ -10236,10 +10239,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>451524</v>
+        <v>451693</v>
       </c>
       <c r="R89" t="n">
-        <v>6795576</v>
+        <v>6795486</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10298,16 +10301,16 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471378</t>
+          <t>https://artportalen.se/Sighting/134471102</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>132724578</v>
+        <v>134471378</v>
       </c>
       <c r="B90" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10315,57 +10318,41 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
-      <c r="N90" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>451910</v>
+        <v>451524</v>
       </c>
       <c r="R90" t="n">
-        <v>6795497</v>
+        <v>6795576</v>
       </c>
       <c r="S90" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10389,12 +10376,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10420,6 +10407,129 @@
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471378</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B91" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S91" t="n">
+        <v>25</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132724578</t>
         </is>
@@ -10516,6 +10626,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4940,7 +4940,7 @@
         <v>137095175</v>
       </c>
       <c r="B41" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4940,7 +4940,7 @@
         <v>137095175</v>
       </c>
       <c r="B41" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4940,7 +4940,7 @@
         <v>137095175</v>
       </c>
       <c r="B41" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4940,7 +4940,7 @@
         <v>137095175</v>
       </c>
       <c r="B41" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -4940,7 +4940,7 @@
         <v>137095175</v>
       </c>
       <c r="B41" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>

--- a/artfynd/A 40996-2023 artfynd.xlsx
+++ b/artfynd/A 40996-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ91"/>
+  <dimension ref="A1:AZ93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,45 +884,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119623805</v>
+        <v>137544793</v>
       </c>
       <c r="B4" t="n">
-        <v>96338</v>
+        <v>83407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2809</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk husmossa</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hylocomiastrum umbratum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) M.Fleisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>451965</v>
+        <v>451690</v>
       </c>
       <c r="R4" t="n">
-        <v>6795388</v>
+        <v>6795479</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -949,12 +952,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -963,30 +966,31 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623805</t>
+          <t>https://artportalen.se/Sighting/137544793</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119624105</v>
+        <v>119623805</v>
       </c>
       <c r="B5" t="n">
         <v>96338</v>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>451926</v>
+        <v>451965</v>
       </c>
       <c r="R5" t="n">
-        <v>6795450</v>
+        <v>6795388</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1059,11 +1063,6 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Kallkällor</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1087,16 +1086,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624105</t>
+          <t>https://artportalen.se/Sighting/119623805</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119623275</v>
+        <v>119624105</v>
       </c>
       <c r="B6" t="n">
-        <v>91680</v>
+        <v>96338</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1104,21 +1103,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3215</v>
+        <v>2809</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Mörk husmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Hylocomiastrum umbratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>(Hedw.) M.Fleisch.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452021</v>
+        <v>451926</v>
       </c>
       <c r="R6" t="n">
-        <v>6795414</v>
+        <v>6795450</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1166,6 +1165,11 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kallkällor</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1189,13 +1193,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623275</t>
+          <t>https://artportalen.se/Sighting/119624105</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119624110</v>
+        <v>119623275</v>
       </c>
       <c r="B7" t="n">
         <v>91680</v>
@@ -1230,10 +1234,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>451915</v>
+        <v>452021</v>
       </c>
       <c r="R7" t="n">
-        <v>6795444</v>
+        <v>6795414</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1291,16 +1295,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624110</t>
+          <t>https://artportalen.se/Sighting/119623275</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119624986</v>
+        <v>119624110</v>
       </c>
       <c r="B8" t="n">
-        <v>92632</v>
+        <v>91680</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1308,34 +1312,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3298</v>
+        <v>3215</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>451575</v>
+        <v>451915</v>
       </c>
       <c r="R8" t="n">
-        <v>6795592</v>
+        <v>6795444</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1393,16 +1397,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624986</t>
+          <t>https://artportalen.se/Sighting/119624110</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119623113</v>
+        <v>119624986</v>
       </c>
       <c r="B9" t="n">
-        <v>92869</v>
+        <v>92632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1410,34 +1414,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4769</v>
+        <v>3298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) Fr.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452038</v>
+        <v>451575</v>
       </c>
       <c r="R9" t="n">
-        <v>6795402</v>
+        <v>6795592</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1495,13 +1499,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623113</t>
+          <t>https://artportalen.se/Sighting/119624986</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>119623309</v>
+        <v>119623113</v>
       </c>
       <c r="B10" t="n">
         <v>92869</v>
@@ -1536,10 +1540,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>451996</v>
+        <v>452038</v>
       </c>
       <c r="R10" t="n">
-        <v>6795413</v>
+        <v>6795402</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,13 +1601,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623309</t>
+          <t>https://artportalen.se/Sighting/119623113</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>119623701</v>
+        <v>119623309</v>
       </c>
       <c r="B11" t="n">
         <v>92869</v>
@@ -1638,10 +1642,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452000</v>
+        <v>451996</v>
       </c>
       <c r="R11" t="n">
-        <v>6795356</v>
+        <v>6795413</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1699,13 +1703,13 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623701</t>
+          <t>https://artportalen.se/Sighting/119623309</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>119624141</v>
+        <v>119623701</v>
       </c>
       <c r="B12" t="n">
         <v>92869</v>
@@ -1740,10 +1744,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>451909</v>
+        <v>452000</v>
       </c>
       <c r="R12" t="n">
-        <v>6795438</v>
+        <v>6795356</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1778,11 +1782,6 @@
           <t>2024-09-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Invid en kallkälla.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1806,16 +1805,16 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624141</t>
+          <t>https://artportalen.se/Sighting/119623701</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>119625094</v>
+        <v>119624141</v>
       </c>
       <c r="B13" t="n">
-        <v>91872</v>
+        <v>92869</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1823,34 +1822,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>4769</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>451529</v>
+        <v>451909</v>
       </c>
       <c r="R13" t="n">
-        <v>6795557</v>
+        <v>6795438</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1885,6 +1884,11 @@
           <t>2024-09-08</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Invid en kallkälla.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -1908,51 +1912,51 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119625094</t>
+          <t>https://artportalen.se/Sighting/119624141</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119623199</v>
+        <v>119625094</v>
       </c>
       <c r="B14" t="n">
-        <v>91443</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5754</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452026</v>
+        <v>451529</v>
       </c>
       <c r="R14" t="n">
-        <v>6795405</v>
+        <v>6795557</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2010,38 +2014,38 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623199</t>
+          <t>https://artportalen.se/Sighting/119625094</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>119623301</v>
+        <v>119623199</v>
       </c>
       <c r="B15" t="n">
-        <v>79327</v>
+        <v>91443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5754</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Corner</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2051,10 +2055,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452006</v>
+        <v>452026</v>
       </c>
       <c r="R15" t="n">
-        <v>6795400</v>
+        <v>6795405</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,13 +2116,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623301</t>
+          <t>https://artportalen.se/Sighting/119623199</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>119624025</v>
+        <v>119623301</v>
       </c>
       <c r="B16" t="n">
         <v>79327</v>
@@ -2153,10 +2157,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>451942</v>
+        <v>452006</v>
       </c>
       <c r="R16" t="n">
-        <v>6795447</v>
+        <v>6795400</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2214,13 +2218,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624025</t>
+          <t>https://artportalen.se/Sighting/119623301</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>119624582</v>
+        <v>119624025</v>
       </c>
       <c r="B17" t="n">
         <v>79327</v>
@@ -2251,14 +2255,14 @@
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Käsdajk, Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>451684</v>
+        <v>451942</v>
       </c>
       <c r="R17" t="n">
-        <v>6795469</v>
+        <v>6795447</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,16 +2320,16 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119624582</t>
+          <t>https://artportalen.se/Sighting/119624025</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135370442</v>
+        <v>119624582</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2351,19 +2355,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>451697</v>
+        <v>451684</v>
       </c>
       <c r="R18" t="n">
-        <v>6795538</v>
+        <v>6795469</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2390,12 +2391,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,31 +2405,30 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370442</t>
+          <t>https://artportalen.se/Sighting/119624582</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135374857</v>
+        <v>135370442</v>
       </c>
       <c r="B19" t="n">
         <v>79441</v>
@@ -2462,14 +2462,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>451506</v>
+        <v>451697</v>
       </c>
       <c r="R19" t="n">
-        <v>6795579</v>
+        <v>6795538</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2528,13 +2528,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135374857</t>
+          <t>https://artportalen.se/Sighting/135370442</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135374874</v>
+        <v>135374857</v>
       </c>
       <c r="B20" t="n">
         <v>79441</v>
@@ -2568,14 +2568,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>451511</v>
+        <v>451506</v>
       </c>
       <c r="R20" t="n">
-        <v>6795591</v>
+        <v>6795579</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2634,59 +2634,57 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135374874</t>
+          <t>https://artportalen.se/Sighting/135374857</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132715558</v>
+        <v>135374874</v>
       </c>
       <c r="B21" t="n">
-        <v>57896</v>
+        <v>79441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100001</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Duvhök</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Astur gentilis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>451683</v>
+        <v>451511</v>
       </c>
       <c r="R21" t="n">
-        <v>6795451</v>
+        <v>6795591</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2710,12 +2708,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2724,50 +2722,51 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132715558</t>
+          <t>https://artportalen.se/Sighting/135374874</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120461420</v>
+        <v>132715558</v>
       </c>
       <c r="B22" t="n">
-        <v>57950</v>
+        <v>57896</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>100001</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Duvhök</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Astur gentilis</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2775,28 +2774,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452004</v>
+        <v>451683</v>
       </c>
       <c r="R22" t="n">
-        <v>6795386</v>
+        <v>6795451</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2820,12 +2816,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2840,27 +2836,27 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120461420</t>
+          <t>https://artportalen.se/Sighting/132715558</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133881553</v>
+        <v>120461420</v>
       </c>
       <c r="B23" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2885,25 +2881,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>451678</v>
+        <v>452004</v>
       </c>
       <c r="R23" t="n">
-        <v>6795601</v>
+        <v>6795386</v>
       </c>
       <c r="S23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2927,27 +2926,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2026-05-27</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>17:29</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Levande gran</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2962,24 +2946,24 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133881553</t>
+          <t>https://artportalen.se/Sighting/120461420</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134471421</v>
+        <v>133881553</v>
       </c>
       <c r="B24" t="n">
         <v>57972</v>
@@ -3008,27 +2992,24 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>451503</v>
+        <v>451678</v>
       </c>
       <c r="R24" t="n">
-        <v>6795552</v>
+        <v>6795601</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3052,12 +3033,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-27</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:29</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Levande gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3072,24 +3068,24 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471421</t>
+          <t>https://artportalen.se/Sighting/133881553</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134471435</v>
+        <v>134471421</v>
       </c>
       <c r="B25" t="n">
         <v>57972</v>
@@ -3132,10 +3128,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>451506</v>
+        <v>451503</v>
       </c>
       <c r="R25" t="n">
-        <v>6795602</v>
+        <v>6795552</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3193,13 +3189,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471435</t>
+          <t>https://artportalen.se/Sighting/134471421</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134519427</v>
+        <v>134471435</v>
       </c>
       <c r="B26" t="n">
         <v>57972</v>
@@ -3228,24 +3224,27 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>451819</v>
+        <v>451506</v>
       </c>
       <c r="R26" t="n">
-        <v>6795533</v>
+        <v>6795602</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3269,22 +3268,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>15:53</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3299,27 +3288,27 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519427</t>
+          <t>https://artportalen.se/Sighting/134471435</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>120461436</v>
+        <v>134519427</v>
       </c>
       <c r="B27" t="n">
-        <v>57945</v>
+        <v>57972</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3327,49 +3316,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100110</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gråspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picus canus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>J.F. Gmelin, 1788</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>451855</v>
+        <v>451819</v>
       </c>
       <c r="R27" t="n">
-        <v>6795436</v>
+        <v>6795533</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3393,12 +3375,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-10-16</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3413,69 +3405,77 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120461436</t>
+          <t>https://artportalen.se/Sighting/134519427</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132752338</v>
+        <v>120461436</v>
       </c>
       <c r="B28" t="n">
-        <v>57835</v>
+        <v>57945</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100136</v>
+        <v>100110</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lappuggla</t>
+          <t>Gråspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Strix nebulosa</t>
+          <t>Picus canus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>J.R. Forster, 1772</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>J.F. Gmelin, 1788</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>451810</v>
+        <v>451855</v>
       </c>
       <c r="R28" t="n">
-        <v>6795373</v>
+        <v>6795436</v>
       </c>
       <c r="S28" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3499,12 +3499,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2024-10-16</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3519,70 +3519,69 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132752338</t>
+          <t>https://artportalen.se/Sighting/120461436</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135260102</v>
+        <v>132752338</v>
       </c>
       <c r="B29" t="n">
-        <v>57167</v>
+        <v>57835</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>100136</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lappuggla</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Strix nebulosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>J.R. Forster, 1772</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>451568</v>
+        <v>451810</v>
       </c>
       <c r="R29" t="n">
-        <v>6795589</v>
+        <v>6795373</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,27 +3605,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>10:19</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>10:19</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Uppflog</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3652,16 +3636,16 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135260102</t>
+          <t>https://artportalen.se/Sighting/132752338</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>120357924</v>
+        <v>135260102</v>
       </c>
       <c r="B30" t="n">
-        <v>57132</v>
+        <v>57167</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3669,49 +3653,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>451903</v>
+        <v>451568</v>
       </c>
       <c r="R30" t="n">
-        <v>6795337</v>
+        <v>6795589</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3735,22 +3712,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-10-12</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>10:19</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Uppflog</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3765,27 +3747,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120357924</t>
+          <t>https://artportalen.se/Sighting/135260102</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>120497002</v>
+        <v>137544868</v>
       </c>
       <c r="B31" t="n">
-        <v>57132</v>
+        <v>57224</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3793,21 +3775,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -3816,11 +3798,7 @@
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+      <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
@@ -3829,10 +3807,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>451667</v>
+        <v>451678</v>
       </c>
       <c r="R31" t="n">
-        <v>6795441</v>
+        <v>6795430</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3859,22 +3837,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2026-10-29</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3900,13 +3868,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120497002</t>
+          <t>https://artportalen.se/Sighting/137544868</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121120126</v>
+        <v>120357924</v>
       </c>
       <c r="B32" t="n">
         <v>57132</v>
@@ -3941,22 +3909,22 @@
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>451990</v>
+        <v>451903</v>
       </c>
       <c r="R32" t="n">
-        <v>6795420</v>
+        <v>6795337</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3983,12 +3951,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-10-12</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4014,16 +3992,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121120126</t>
+          <t>https://artportalen.se/Sighting/120357924</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134519429</v>
+        <v>120497002</v>
       </c>
       <c r="B33" t="n">
-        <v>57153</v>
+        <v>57132</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4048,25 +4026,32 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>451845</v>
+        <v>451667</v>
       </c>
       <c r="R33" t="n">
-        <v>6795506</v>
+        <v>6795441</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4090,22 +4075,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4120,44 +4105,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519429</t>
+          <t>https://artportalen.se/Sighting/120497002</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136240267</v>
+        <v>121120126</v>
       </c>
       <c r="B34" t="n">
-        <v>57849</v>
+        <v>57132</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4165,25 +4150,29 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452004</v>
+        <v>451990</v>
       </c>
       <c r="R34" t="n">
-        <v>6795386</v>
+        <v>6795420</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4210,12 +4199,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4241,63 +4230,59 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136240267</t>
+          <t>https://artportalen.se/Sighting/121120126</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132667638</v>
+        <v>134519429</v>
       </c>
       <c r="B35" t="n">
-        <v>58410</v>
+        <v>57153</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103001</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>besöker bebott bo</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452007</v>
+        <v>451845</v>
       </c>
       <c r="R35" t="n">
-        <v>6795396</v>
+        <v>6795506</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4321,12 +4306,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-04-21</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4352,33 +4347,33 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132667638</t>
+          <t>https://artportalen.se/Sighting/134519429</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133881550</v>
+        <v>136240267</v>
       </c>
       <c r="B36" t="n">
-        <v>58349</v>
+        <v>57849</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103015</v>
+        <v>102621</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4387,21 +4382,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>451505</v>
+        <v>452004</v>
       </c>
       <c r="R36" t="n">
-        <v>6795559</v>
+        <v>6795386</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4428,22 +4426,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:42</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4458,27 +4446,27 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133881550</t>
+          <t>https://artportalen.se/Sighting/136240267</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122780415</v>
+        <v>132667638</v>
       </c>
       <c r="B37" t="n">
-        <v>58114</v>
+        <v>58410</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4486,53 +4474,46 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>451903</v>
+        <v>452007</v>
       </c>
       <c r="R37" t="n">
-        <v>6795337</v>
+        <v>6795396</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4556,22 +4537,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4586,81 +4557,70 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780415</t>
+          <t>https://artportalen.se/Sighting/132667638</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132477046</v>
+        <v>133881550</v>
       </c>
       <c r="B38" t="n">
-        <v>58136</v>
+        <v>58349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
           <t>spel/sång</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>451648</v>
+        <v>451505</v>
       </c>
       <c r="R38" t="n">
-        <v>6795608</v>
+        <v>6795559</v>
       </c>
       <c r="S38" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4684,12 +4644,22 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4704,27 +4674,27 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477046</t>
+          <t>https://artportalen.se/Sighting/133881550</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134471194</v>
+        <v>122780415</v>
       </c>
       <c r="B39" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4749,25 +4719,33 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>451635</v>
+        <v>451903</v>
       </c>
       <c r="R39" t="n">
-        <v>6795544</v>
+        <v>6795337</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4794,12 +4772,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4825,16 +4813,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471194</t>
+          <t>https://artportalen.se/Sighting/122780415</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135940024</v>
+        <v>132477046</v>
       </c>
       <c r="B40" t="n">
-        <v>58167</v>
+        <v>58136</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4859,24 +4847,36 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>451757</v>
+        <v>451648</v>
       </c>
       <c r="R40" t="n">
-        <v>6795445</v>
+        <v>6795608</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4931,16 +4931,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135940024</t>
+          <t>https://artportalen.se/Sighting/132477046</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>137095175</v>
+        <v>134471194</v>
       </c>
       <c r="B41" t="n">
-        <v>58196</v>
+        <v>58136</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4965,25 +4965,25 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>451853</v>
+        <v>451635</v>
       </c>
       <c r="R41" t="n">
-        <v>6795315</v>
+        <v>6795544</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5010,12 +5010,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5041,66 +5041,58 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137095175</t>
+          <t>https://artportalen.se/Sighting/134471194</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>132477079</v>
+        <v>135940024</v>
       </c>
       <c r="B42" t="n">
-        <v>58131</v>
+        <v>58167</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>103023</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>451648</v>
+        <v>451757</v>
       </c>
       <c r="R42" t="n">
-        <v>6795608</v>
+        <v>6795445</v>
       </c>
       <c r="S42" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5124,12 +5116,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5155,16 +5147,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477079</t>
+          <t>https://artportalen.se/Sighting/135940024</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>125109158</v>
+        <v>137095175</v>
       </c>
       <c r="B43" t="n">
-        <v>56522</v>
+        <v>58199</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5172,49 +5164,45 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>451891</v>
+        <v>451853</v>
       </c>
       <c r="R43" t="n">
-        <v>6795458</v>
+        <v>6795315</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5238,12 +5226,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5269,52 +5257,48 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125109158</t>
+          <t>https://artportalen.se/Sighting/137095175</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>132477114</v>
+        <v>132477079</v>
       </c>
       <c r="B44" t="n">
-        <v>56539</v>
+        <v>58131</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>206004</v>
+        <v>103023</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>gående/springande</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -5387,33 +5371,33 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132477114</t>
+          <t>https://artportalen.se/Sighting/132477079</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>132918321</v>
+        <v>125109158</v>
       </c>
       <c r="B45" t="n">
-        <v>58839</v>
+        <v>56522</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>208249</v>
+        <v>206004</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5423,32 +5407,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>451860</v>
+        <v>451891</v>
       </c>
       <c r="R45" t="n">
-        <v>6795469</v>
+        <v>6795458</v>
       </c>
       <c r="S45" t="n">
         <v>25</v>
@@ -5475,12 +5454,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5489,7 +5468,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5507,62 +5485,70 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132918321</t>
+          <t>https://artportalen.se/Sighting/125109158</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134446393</v>
+        <v>132477114</v>
       </c>
       <c r="B46" t="n">
-        <v>99103</v>
+        <v>56539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>219788</v>
+        <v>206004</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ängsnycklar</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dactylorhiza incarnata</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>gående/springande</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>451856</v>
+        <v>451648</v>
       </c>
       <c r="R46" t="n">
-        <v>6795459</v>
+        <v>6795608</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5586,12 +5572,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5600,7 +5586,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5618,16 +5603,16 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446393</t>
+          <t>https://artportalen.se/Sighting/132477114</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133997108</v>
+        <v>132918321</v>
       </c>
       <c r="B47" t="n">
-        <v>99112</v>
+        <v>58839</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,38 +5620,51 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219790</v>
+        <v>208249</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>451891</v>
+        <v>451860</v>
       </c>
       <c r="R47" t="n">
-        <v>6795458</v>
+        <v>6795469</v>
       </c>
       <c r="S47" t="n">
         <v>25</v>
@@ -5693,12 +5691,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5725,16 +5723,16 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997108</t>
+          <t>https://artportalen.se/Sighting/132918321</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133997151</v>
+        <v>134446393</v>
       </c>
       <c r="B48" t="n">
-        <v>99112</v>
+        <v>99103</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5742,16 +5740,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219790</v>
+        <v>219788</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Ängsnycklar</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Dactylorhiza incarnata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -5761,7 +5759,11 @@
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
@@ -5770,10 +5772,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>451900</v>
+        <v>451856</v>
       </c>
       <c r="R48" t="n">
-        <v>6795487</v>
+        <v>6795459</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5800,12 +5802,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5832,13 +5834,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997151</t>
+          <t>https://artportalen.se/Sighting/134446393</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134446465</v>
+        <v>133997108</v>
       </c>
       <c r="B49" t="n">
         <v>99112</v>
@@ -5868,11 +5870,7 @@
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
@@ -5881,13 +5879,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>451867</v>
+        <v>451891</v>
       </c>
       <c r="R49" t="n">
-        <v>6795467</v>
+        <v>6795458</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5911,12 +5909,12 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5943,13 +5941,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446465</t>
+          <t>https://artportalen.se/Sighting/133997108</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134452196</v>
+        <v>133997151</v>
       </c>
       <c r="B50" t="n">
         <v>99112</v>
@@ -5984,14 +5982,14 @@
       <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>451858</v>
+        <v>451900</v>
       </c>
       <c r="R50" t="n">
-        <v>6795529</v>
+        <v>6795487</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6018,12 +6016,12 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6050,13 +6048,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452196</t>
+          <t>https://artportalen.se/Sighting/133997151</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134452278</v>
+        <v>134446465</v>
       </c>
       <c r="B51" t="n">
         <v>99112</v>
@@ -6086,7 +6084,11 @@
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
@@ -6095,10 +6097,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>451878</v>
+        <v>451867</v>
       </c>
       <c r="R51" t="n">
-        <v>6795529</v>
+        <v>6795467</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6157,13 +6159,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452278</t>
+          <t>https://artportalen.se/Sighting/134446465</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134452340</v>
+        <v>134452196</v>
       </c>
       <c r="B52" t="n">
         <v>99112</v>
@@ -6202,10 +6204,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>451934</v>
+        <v>451858</v>
       </c>
       <c r="R52" t="n">
-        <v>6795489</v>
+        <v>6795529</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6264,13 +6266,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452340</t>
+          <t>https://artportalen.se/Sighting/134452196</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134452392</v>
+        <v>134452278</v>
       </c>
       <c r="B53" t="n">
         <v>99112</v>
@@ -6309,10 +6311,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>451845</v>
+        <v>451878</v>
       </c>
       <c r="R53" t="n">
-        <v>6795346</v>
+        <v>6795529</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6371,13 +6373,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452392</t>
+          <t>https://artportalen.se/Sighting/134452278</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134452446</v>
+        <v>134452340</v>
       </c>
       <c r="B54" t="n">
         <v>99112</v>
@@ -6416,10 +6418,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>451876</v>
+        <v>451934</v>
       </c>
       <c r="R54" t="n">
-        <v>6795437</v>
+        <v>6795489</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6478,13 +6480,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452446</t>
+          <t>https://artportalen.se/Sighting/134452340</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134452468</v>
+        <v>134452392</v>
       </c>
       <c r="B55" t="n">
         <v>99112</v>
@@ -6523,10 +6525,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>451872</v>
+        <v>451845</v>
       </c>
       <c r="R55" t="n">
-        <v>6795459</v>
+        <v>6795346</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6585,13 +6587,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452468</t>
+          <t>https://artportalen.se/Sighting/134452392</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134470975</v>
+        <v>134452446</v>
       </c>
       <c r="B56" t="n">
         <v>99112</v>
@@ -6619,33 +6621,21 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>451828</v>
+        <v>451876</v>
       </c>
       <c r="R56" t="n">
-        <v>6795362</v>
+        <v>6795437</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6672,12 +6662,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6704,13 +6694,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470975</t>
+          <t>https://artportalen.se/Sighting/134452446</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134471030</v>
+        <v>134452468</v>
       </c>
       <c r="B57" t="n">
         <v>99112</v>
@@ -6749,10 +6739,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>451822</v>
+        <v>451872</v>
       </c>
       <c r="R57" t="n">
-        <v>6795403</v>
+        <v>6795459</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6779,12 +6769,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6811,13 +6801,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471030</t>
+          <t>https://artportalen.se/Sighting/134452468</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134471064</v>
+        <v>134470975</v>
       </c>
       <c r="B58" t="n">
         <v>99112</v>
@@ -6845,21 +6835,33 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>451754</v>
+        <v>451828</v>
       </c>
       <c r="R58" t="n">
-        <v>6795474</v>
+        <v>6795362</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6918,13 +6920,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471064</t>
+          <t>https://artportalen.se/Sighting/134470975</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>134471377</v>
+        <v>134471030</v>
       </c>
       <c r="B59" t="n">
         <v>99112</v>
@@ -6963,10 +6965,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>451524</v>
+        <v>451822</v>
       </c>
       <c r="R59" t="n">
-        <v>6795576</v>
+        <v>6795403</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7025,13 +7027,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471377</t>
+          <t>https://artportalen.se/Sighting/134471030</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>134519430</v>
+        <v>134471064</v>
       </c>
       <c r="B60" t="n">
         <v>99112</v>
@@ -7060,19 +7062,23 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>451846</v>
+        <v>451754</v>
       </c>
       <c r="R60" t="n">
-        <v>6795506</v>
+        <v>6795474</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7096,22 +7102,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:58</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7120,33 +7116,34 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519430</t>
+          <t>https://artportalen.se/Sighting/134471064</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135087727</v>
+        <v>134471377</v>
       </c>
       <c r="B61" t="n">
-        <v>99186</v>
+        <v>99112</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7178,14 +7175,14 @@
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>451853</v>
+        <v>451524</v>
       </c>
       <c r="R61" t="n">
-        <v>6795315</v>
+        <v>6795576</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7212,12 +7209,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7244,16 +7241,16 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135087727</t>
+          <t>https://artportalen.se/Sighting/134471377</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135940067</v>
+        <v>134519430</v>
       </c>
       <c r="B62" t="n">
-        <v>99259</v>
+        <v>99112</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7278,32 +7275,20 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>451650</v>
+        <v>451846</v>
       </c>
       <c r="R62" t="n">
-        <v>6795625</v>
+        <v>6795506</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7327,12 +7312,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7341,34 +7336,33 @@
       <c r="AE62" t="b">
         <v>0</v>
       </c>
-      <c r="AF62" t="inlineStr"/>
       <c r="AG62" t="b">
         <v>0</v>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135940067</t>
+          <t>https://artportalen.se/Sighting/134519430</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135370390</v>
+        <v>135087727</v>
       </c>
       <c r="B63" t="n">
-        <v>99175</v>
+        <v>99186</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7376,42 +7370,38 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Gambelyöllander, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>451924</v>
+        <v>451853</v>
       </c>
       <c r="R63" t="n">
-        <v>6795456</v>
+        <v>6795315</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7438,17 +7428,12 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>I källmiljö</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7475,16 +7460,16 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370390</t>
+          <t>https://artportalen.se/Sighting/135087727</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135896094</v>
+        <v>135940067</v>
       </c>
       <c r="B64" t="n">
-        <v>99241</v>
+        <v>99259</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7492,38 +7477,46 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>219795</v>
+        <v>219790</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Grönkulla</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Coeloglossum viride</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hartm.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>451940</v>
+        <v>451650</v>
       </c>
       <c r="R64" t="n">
-        <v>6795495</v>
+        <v>6795625</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7550,12 +7543,12 @@
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7582,16 +7575,16 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896094</t>
+          <t>https://artportalen.se/Sighting/135940067</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135384823</v>
+        <v>135370390</v>
       </c>
       <c r="B65" t="n">
-        <v>108294</v>
+        <v>99175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7599,38 +7592,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220083</v>
+        <v>219795</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>451640</v>
+        <v>451924</v>
       </c>
       <c r="R65" t="n">
-        <v>6795589</v>
+        <v>6795456</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7667,7 +7664,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Invid källbäck</t>
+          <t>I källmiljö</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7694,16 +7691,16 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135384823</t>
+          <t>https://artportalen.se/Sighting/135370390</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>134446457</v>
+        <v>135896094</v>
       </c>
       <c r="B66" t="n">
-        <v>99099</v>
+        <v>99241</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7711,42 +7708,38 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220093</v>
+        <v>219795</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Grönkulla</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Coeloglossum viride</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hartm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>451867</v>
+        <v>451940</v>
       </c>
       <c r="R66" t="n">
-        <v>6795467</v>
+        <v>6795495</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7773,12 +7766,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7805,16 +7798,16 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134446457</t>
+          <t>https://artportalen.se/Sighting/135896094</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>134452308</v>
+        <v>135384823</v>
       </c>
       <c r="B67" t="n">
-        <v>99099</v>
+        <v>108294</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7822,30 +7815,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220093</v>
+        <v>220083</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallrot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Corallorhiza trifida</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Châtel.</t>
+          <t>(L.) Hill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
@@ -7854,10 +7843,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>451924</v>
+        <v>451640</v>
       </c>
       <c r="R67" t="n">
-        <v>6795490</v>
+        <v>6795589</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7884,12 +7873,17 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Invid källbäck</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7916,13 +7910,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452308</t>
+          <t>https://artportalen.se/Sighting/135384823</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>134471116</v>
+        <v>134446457</v>
       </c>
       <c r="B68" t="n">
         <v>99099</v>
@@ -7952,7 +7946,11 @@
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -7961,10 +7959,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>451657</v>
+        <v>451867</v>
       </c>
       <c r="R68" t="n">
-        <v>6795504</v>
+        <v>6795467</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7991,12 +7989,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8023,13 +8021,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471116</t>
+          <t>https://artportalen.se/Sighting/134446457</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>134471163</v>
+        <v>134452308</v>
       </c>
       <c r="B69" t="n">
         <v>99099</v>
@@ -8059,7 +8057,11 @@
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
@@ -8068,10 +8070,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>451656</v>
+        <v>451924</v>
       </c>
       <c r="R69" t="n">
-        <v>6795514</v>
+        <v>6795490</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8098,12 +8100,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8130,13 +8132,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471163</t>
+          <t>https://artportalen.se/Sighting/134452308</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>134471374</v>
+        <v>134471116</v>
       </c>
       <c r="B70" t="n">
         <v>99099</v>
@@ -8175,10 +8177,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>451524</v>
+        <v>451657</v>
       </c>
       <c r="R70" t="n">
-        <v>6795576</v>
+        <v>6795504</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8237,16 +8239,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471374</t>
+          <t>https://artportalen.se/Sighting/134471116</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>134471215</v>
+        <v>134471163</v>
       </c>
       <c r="B71" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8254,21 +8256,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8278,14 +8280,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>451641</v>
+        <v>451656</v>
       </c>
       <c r="R71" t="n">
-        <v>6795575</v>
+        <v>6795514</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8344,16 +8346,16 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471215</t>
+          <t>https://artportalen.se/Sighting/134471163</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>134471223</v>
+        <v>134471374</v>
       </c>
       <c r="B72" t="n">
-        <v>108274</v>
+        <v>99099</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8361,21 +8363,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220102</v>
+        <v>220093</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kärrfibbla</t>
+          <t>Korallrot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Crepis paludosa</t>
+          <t>Corallorhiza trifida</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Moench</t>
+          <t>Châtel.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8389,10 +8391,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>451640</v>
+        <v>451524</v>
       </c>
       <c r="R72" t="n">
-        <v>6795589</v>
+        <v>6795576</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8451,13 +8453,13 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471223</t>
+          <t>https://artportalen.se/Sighting/134471374</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134471252</v>
+        <v>134471215</v>
       </c>
       <c r="B73" t="n">
         <v>108274</v>
@@ -8492,14 +8494,14 @@
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>451628</v>
+        <v>451641</v>
       </c>
       <c r="R73" t="n">
-        <v>6795600</v>
+        <v>6795575</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8558,60 +8560,55 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471252</t>
+          <t>https://artportalen.se/Sighting/134471215</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119623430</v>
+        <v>134471223</v>
       </c>
       <c r="B74" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>452010</v>
+        <v>451640</v>
       </c>
       <c r="R74" t="n">
-        <v>6795395</v>
+        <v>6795589</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8638,12 +8635,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8652,80 +8649,73 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623430</t>
+          <t>https://artportalen.se/Sighting/134471223</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120455163</v>
+        <v>134471252</v>
       </c>
       <c r="B75" t="n">
-        <v>99118</v>
+        <v>108274</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>220102</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kärrfibbla</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crepis paludosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Moench</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>452004</v>
+        <v>451628</v>
       </c>
       <c r="R75" t="n">
-        <v>6795386</v>
+        <v>6795600</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8752,12 +8742,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8784,13 +8774,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120455163</t>
+          <t>https://artportalen.se/Sighting/134471252</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120493954</v>
+        <v>119623430</v>
       </c>
       <c r="B76" t="n">
         <v>99118</v>
@@ -8820,7 +8810,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -8828,19 +8818,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>451990</v>
+        <v>452010</v>
       </c>
       <c r="R76" t="n">
-        <v>6795420</v>
+        <v>6795395</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8867,12 +8854,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-10-19</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8881,34 +8868,33 @@
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120493954</t>
+          <t>https://artportalen.se/Sighting/119623430</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133997095</v>
+        <v>120455163</v>
       </c>
       <c r="B77" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8935,12 +8921,12 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -8948,14 +8934,14 @@
       <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd , Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>451903</v>
+        <v>452004</v>
       </c>
       <c r="R77" t="n">
-        <v>6795472</v>
+        <v>6795386</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8982,12 +8968,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9014,16 +9000,16 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997095</t>
+          <t>https://artportalen.se/Sighting/120455163</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133997219</v>
+        <v>120493954</v>
       </c>
       <c r="B78" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9050,12 +9036,12 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
@@ -9063,14 +9049,14 @@
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>451888</v>
+        <v>451990</v>
       </c>
       <c r="R78" t="n">
-        <v>6795475</v>
+        <v>6795420</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9097,12 +9083,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2024-10-19</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9129,51 +9115,63 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133997219</t>
+          <t>https://artportalen.se/Sighting/120493954</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119622912</v>
+        <v>133997095</v>
       </c>
       <c r="B79" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>452035</v>
+        <v>451903</v>
       </c>
       <c r="R79" t="n">
-        <v>6795377</v>
+        <v>6795472</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9200,12 +9198,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9214,68 +9212,81 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119622912</t>
+          <t>https://artportalen.se/Sighting/133997095</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119623971</v>
+        <v>133997219</v>
       </c>
       <c r="B80" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Övergärd, Övergärd, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>451957</v>
+        <v>451888</v>
       </c>
       <c r="R80" t="n">
-        <v>6795424</v>
+        <v>6795475</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9302,12 +9313,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-08</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9316,33 +9327,34 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Sebastian Kirppu</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119623971</t>
+          <t>https://artportalen.se/Sighting/133997219</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>135896078</v>
+        <v>119622912</v>
       </c>
       <c r="B81" t="n">
-        <v>106468</v>
+        <v>106229</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9368,20 +9380,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>452073</v>
+        <v>452035</v>
       </c>
       <c r="R81" t="n">
-        <v>6795385</v>
+        <v>6795377</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9408,12 +9416,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9422,34 +9430,33 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135896078</t>
+          <t>https://artportalen.se/Sighting/119622912</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134452234</v>
+        <v>119623971</v>
       </c>
       <c r="B82" t="n">
-        <v>98060</v>
+        <v>106229</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9457,38 +9464,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>451878</v>
+        <v>451957</v>
       </c>
       <c r="R82" t="n">
-        <v>6795529</v>
+        <v>6795424</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9515,12 +9518,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-09-08</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9529,34 +9532,33 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Sebastian Kirppu</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452234</t>
+          <t>https://artportalen.se/Sighting/119623971</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>134452406</v>
+        <v>135896078</v>
       </c>
       <c r="B83" t="n">
-        <v>98060</v>
+        <v>106468</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9564,21 +9566,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>221945</v>
+        <v>221725</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9588,14 +9590,14 @@
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Övergärd, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>451858</v>
+        <v>452073</v>
       </c>
       <c r="R83" t="n">
-        <v>6795410</v>
+        <v>6795385</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9622,12 +9624,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9654,13 +9656,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452406</t>
+          <t>https://artportalen.se/Sighting/135896078</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>134452426</v>
+        <v>134452234</v>
       </c>
       <c r="B84" t="n">
         <v>98060</v>
@@ -9699,10 +9701,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>451875</v>
+        <v>451878</v>
       </c>
       <c r="R84" t="n">
-        <v>6795422</v>
+        <v>6795529</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9761,13 +9763,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134452426</t>
+          <t>https://artportalen.se/Sighting/134452234</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>134519426</v>
+        <v>134452406</v>
       </c>
       <c r="B85" t="n">
         <v>98060</v>
@@ -9796,19 +9798,23 @@
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Käsdajk-Övergärd, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>451669</v>
+        <v>451858</v>
       </c>
       <c r="R85" t="n">
-        <v>6795570</v>
+        <v>6795410</v>
       </c>
       <c r="S85" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9832,22 +9838,12 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>15:43</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9856,33 +9852,34 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Jenni Arvidsson</t>
+          <t>Gunnar Åhs</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134519426</t>
+          <t>https://artportalen.se/Sighting/134452406</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>135370746</v>
+        <v>134452426</v>
       </c>
       <c r="B86" t="n">
-        <v>98138</v>
+        <v>98060</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9914,14 +9911,14 @@
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
+          <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>451924</v>
+        <v>451875</v>
       </c>
       <c r="R86" t="n">
-        <v>6795456</v>
+        <v>6795422</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9948,12 +9945,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9980,16 +9977,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370746</t>
+          <t>https://artportalen.se/Sighting/134452426</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>135370757</v>
+        <v>134519426</v>
       </c>
       <c r="B87" t="n">
-        <v>98138</v>
+        <v>98060</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10015,23 +10012,19 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk-Övergärd, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>451910</v>
+        <v>451669</v>
       </c>
       <c r="R87" t="n">
-        <v>6795497</v>
+        <v>6795570</v>
       </c>
       <c r="S87" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10055,12 +10048,22 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10069,34 +10072,33 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Gunnar Åhs</t>
+          <t>Jenni Arvidsson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135370757</t>
+          <t>https://artportalen.se/Sighting/134519426</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>134470979</v>
+        <v>135370746</v>
       </c>
       <c r="B88" t="n">
-        <v>99217</v>
+        <v>98138</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10104,21 +10106,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10132,10 +10134,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>451828</v>
+        <v>451924</v>
       </c>
       <c r="R88" t="n">
-        <v>6795362</v>
+        <v>6795456</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10162,12 +10164,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10194,16 +10196,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134470979</t>
+          <t>https://artportalen.se/Sighting/135370746</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134471102</v>
+        <v>135370757</v>
       </c>
       <c r="B89" t="n">
-        <v>99217</v>
+        <v>98138</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10211,21 +10213,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>221952</v>
+        <v>221945</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10239,13 +10241,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>451693</v>
+        <v>451910</v>
       </c>
       <c r="R89" t="n">
-        <v>6795486</v>
+        <v>6795497</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10269,12 +10271,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10301,13 +10303,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471102</t>
+          <t>https://artportalen.se/Sighting/135370757</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>134471378</v>
+        <v>134470979</v>
       </c>
       <c r="B90" t="n">
         <v>99217</v>
@@ -10342,14 +10344,14 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Käsdajk, Dlr</t>
+          <t>Käsdajk, Klitten, Älvdalen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>451524</v>
+        <v>451828</v>
       </c>
       <c r="R90" t="n">
-        <v>6795576</v>
+        <v>6795362</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10408,16 +10410,16 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134471378</t>
+          <t>https://artportalen.se/Sighting/134470979</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>132724578</v>
+        <v>134471102</v>
       </c>
       <c r="B91" t="n">
-        <v>101403</v>
+        <v>99217</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10425,57 +10427,41 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>222498</v>
+        <v>221952</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Käsdajk, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>451910</v>
+        <v>451693</v>
       </c>
       <c r="R91" t="n">
-        <v>6795497</v>
+        <v>6795486</v>
       </c>
       <c r="S91" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10499,12 +10485,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10530,6 +10516,236 @@
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471102</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>134471378</v>
+      </c>
+      <c r="B92" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>451524</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6795576</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134471378</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>132724578</v>
+      </c>
+      <c r="B93" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Käsdajk, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>451910</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6795497</v>
+      </c>
+      <c r="S93" t="n">
+        <v>25</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Älvdalen</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF93" t="inlineStr"/>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Gunnar Åhs</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132724578</t>
         </is>
@@ -10627,6 +10843,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
